--- a/Account/Account Details Nov.xlsx
+++ b/Account/Account Details Nov.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Account Details November" sheetId="2" r:id="rId2"/>
+    <sheet name="Account Details Dec" sheetId="3" r:id="rId2"/>
+    <sheet name="Account Details Jan" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="53">
   <si>
     <t xml:space="preserve">ACCOUNT NAME </t>
   </si>
@@ -58,16 +59,18 @@
     <t>KATHIRAVAN</t>
   </si>
   <si>
-    <t>(1L Credit from karthick s)
-(50k credit from Ashwin raj)
-(20k credit from Karthick s)    
-(1L credit from Yoganathan)
-(1L Credit from Yoganathan)</t>
+    <t xml:space="preserve">
+50k - Credit from Soundarya
+2.5k - Credit from Mukesh
+1092 - </t>
   </si>
   <si>
     <t>Nil</t>
   </si>
   <si>
+    <t>3,29,130</t>
+  </si>
+  <si>
     <t>RANJANI</t>
   </si>
   <si>
@@ -80,8 +83,9 @@
     <t xml:space="preserve">AJITH SURYA </t>
   </si>
   <si>
-    <t>(1.4L Credit from Soundarya )
-(1.2L-Credit from Mukesh)</t>
+    <t xml:space="preserve">(1.4L Credit from Soundarya )
+(1.2L-Credit from Mukesh)
+</t>
   </si>
   <si>
     <t>3,75,544</t>
@@ -96,49 +100,122 @@
     <t>AMOUNT DEBITED</t>
   </si>
   <si>
+    <t xml:space="preserve">Aathi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50k- Credit fromTamil Prbha 
+40k- Credit from Vishaka Kumar 
+50k - Credit from Vishaka Kumar 
+80k - Credit from Sanjay Subramanian
+1L - Credit from Bousika 
+20k - Credit from Bousika 
+90k - Credit from Sanjay Subramanian
+80k - Credit from Sanjay Subramanian 
+40K - Credit from Pradeep 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1L- Transfer to Pradeep Rajendran 
+50k transfer to stephen raj
+ 1l -transfer to lokesh
+52800- Transfer to Prathiba Karan 
+20k - Transfer to Praveen Kumar </t>
+  </si>
+  <si>
+    <t>2,57,772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajith Surya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+50k - Credit from Soundarya
+2.5k - Credit from Mukesh
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1L - Debited to Virtusa HR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathiravan </t>
+  </si>
+  <si>
+    <t>20k-Credit from Ashwin Raj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60k - Transfer to Stephen Raj 
+50k - Transfer to Virtusa HR </t>
+  </si>
+  <si>
+    <t>3,41,592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranjani Neelakandan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2L - Credit from P riyanka 
+1L - Credit from Priyanka 
+30k Credit from Javeed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10L - Transfer to Lokesh </t>
+  </si>
+  <si>
+    <t>4,35,083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sriram </t>
+  </si>
+  <si>
+    <t>122500 - Credit from Mukesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5L - Dedited to Virtusa HR For Priyanka </t>
+  </si>
+  <si>
+    <t>4,19,319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramesh Durai </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50k - Credit from Vishaka Kumar </t>
+  </si>
+  <si>
+    <t>1.5L - Debited to Ajith surya Canara Account</t>
+  </si>
+  <si>
+    <t>3,78,827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMOUNT CREDITED </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMOUNT DEBITED </t>
+  </si>
+  <si>
     <t>ACCOUNT BALANCE</t>
   </si>
   <si>
-    <t>50k-Credit from Tamil prabha
-40k-Credit from Vishaka kumar
-50k-Credit from Vishaka kumar 
-80k-Credit from Sanjay subramanian 
-1L-Credit from Bousika
-20k-Credit from Bousika 
-90k-Sanjay subramanian 
-80k-Sanjay subramanian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1L- Transfer to Pradeep Rajendran </t>
-  </si>
-  <si>
-    <t>AJITH SURYA</t>
-  </si>
-  <si>
-    <t>1.10L-Credit from Soundarya</t>
-  </si>
-  <si>
-    <t>4,28,045</t>
-  </si>
-  <si>
-    <t>20k-Credit from Ashwin Raj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60k-Transfer to Stephen Raj </t>
-  </si>
-  <si>
-    <t>3,90,000</t>
-  </si>
-  <si>
-    <t>2L-Credit from Priyanka
-1L-Credit from Priyanka
-30k-Credit from Javeed</t>
-  </si>
-  <si>
-    <t>5,43,422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5L - Handover to Virtusa HR </t>
+    <t>Aathi</t>
+  </si>
+  <si>
+    <t>Ajith Surya</t>
+  </si>
+  <si>
+    <t>Kathiravan</t>
+  </si>
+  <si>
+    <t>60k - Credit from Vishaka Kumar</t>
+  </si>
+  <si>
+    <t>4,79,319</t>
+  </si>
+  <si>
+    <t>Ranjani Neelakandan</t>
+  </si>
+  <si>
+    <t>Ramesh Durai</t>
   </si>
 </sst>
 </file>
@@ -760,23 +837,35 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1103,152 +1192,152 @@
   <cols>
     <col min="1" max="1" width="15.2685185185185" customWidth="1"/>
     <col min="2" max="2" width="39.8148148148148" customWidth="1"/>
-    <col min="3" max="3" width="27.2685185185185" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.8148148148148" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.2685185185185" style="6" customWidth="1"/>
+    <col min="4" max="4" width="17.8148148148148" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="57.6" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="10">
         <v>445029</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" ht="72" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" ht="57.6" spans="1:7">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2">
-        <v>430000</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="10">
         <v>213422</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="10">
         <v>476129</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="28.8" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" ht="43.2" spans="1:7">
+      <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:24">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7">
         <v>10000</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="X7" s="7" t="s">
-        <v>17</v>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="X7" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1259,150 +1348,152 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H74"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="34.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="33.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="18.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="37.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="17.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" ht="115.2" spans="1:9">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" ht="144" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="4">
-        <v>420000</v>
+      <c r="C2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9">
+    </row>
+    <row r="3" ht="57.6" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9">
+    </row>
+    <row r="4" ht="28.8" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" ht="43.2" spans="1:9">
+    </row>
+    <row r="5" ht="43.2" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9">
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="2">
-        <v>295029</v>
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2">
-        <v>476129</v>
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9">
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9">
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1411,9 +1502,8 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9">
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1422,9 +1512,8 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9">
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1433,9 +1522,8 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9">
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1444,9 +1532,8 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9">
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1455,9 +1542,8 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9">
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1466,9 +1552,8 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9">
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1477,9 +1562,8 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9">
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1488,9 +1572,8 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9">
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1499,9 +1582,8 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9">
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1510,9 +1592,8 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9">
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1521,9 +1602,8 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9">
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1532,9 +1612,8 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9">
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1543,9 +1622,8 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9">
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1554,9 +1632,8 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9">
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1565,9 +1642,8 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9">
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1576,7 +1652,625 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="19.3333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.4444444444444" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.3333333333333" style="2" customWidth="1"/>
+    <col min="5" max="6" width="8.88888888888889" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
